--- a/Team-Data/2014-15/1-26-2014-15.xlsx
+++ b/Team-Data/2014-15/1-26-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>7.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -751,7 +818,7 @@
         <v>2</v>
       </c>
       <c r="AH2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI2" t="n">
         <v>11</v>
@@ -775,7 +842,7 @@
         <v>13</v>
       </c>
       <c r="AP2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ2" t="n">
         <v>8</v>
@@ -793,7 +860,7 @@
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW2" t="n">
         <v>5</v>
@@ -814,7 +881,7 @@
         <v>6</v>
       </c>
       <c r="BC2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-26-2014-15</t>
+          <t>2015-01-26</t>
         </is>
       </c>
     </row>
@@ -843,58 +910,58 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>27</v>
       </c>
       <c r="G3" t="n">
-        <v>0.372</v>
+        <v>0.357</v>
       </c>
       <c r="H3" t="n">
         <v>48.6</v>
       </c>
       <c r="I3" t="n">
-        <v>39.6</v>
+        <v>39.7</v>
       </c>
       <c r="J3" t="n">
-        <v>87.59999999999999</v>
+        <v>88</v>
       </c>
       <c r="K3" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L3" t="n">
         <v>7.6</v>
       </c>
       <c r="M3" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.331</v>
+        <v>0.33</v>
       </c>
       <c r="O3" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="P3" t="n">
         <v>19.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.756</v>
+        <v>0.752</v>
       </c>
       <c r="R3" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="S3" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="T3" t="n">
-        <v>43.3</v>
+        <v>43.5</v>
       </c>
       <c r="U3" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="V3" t="n">
         <v>14.6</v>
@@ -906,31 +973,31 @@
         <v>4.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="AB3" t="n">
         <v>101.9</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1.7</v>
+        <v>-2</v>
       </c>
       <c r="AD3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE3" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AF3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AH3" t="n">
         <v>6</v>
@@ -942,7 +1009,7 @@
         <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL3" t="n">
         <v>13</v>
@@ -960,19 +1027,19 @@
         <v>27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AR3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AS3" t="n">
         <v>12</v>
       </c>
       <c r="AT3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV3" t="n">
         <v>16</v>
@@ -984,10 +1051,10 @@
         <v>26</v>
       </c>
       <c r="AY3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AZ3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA3" t="n">
         <v>30</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-26-2014-15</t>
+          <t>2015-01-26</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-3.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
         <v>19</v>
@@ -1142,7 +1209,7 @@
         <v>21</v>
       </c>
       <c r="AQ4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR4" t="n">
         <v>26</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-26-2014-15</t>
+          <t>2015-01-26</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-2.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE5" t="n">
         <v>18</v>
@@ -1324,7 +1391,7 @@
         <v>12</v>
       </c>
       <c r="AQ5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR5" t="n">
         <v>21</v>
@@ -1333,7 +1400,7 @@
         <v>7</v>
       </c>
       <c r="AT5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU5" t="n">
         <v>27</v>
@@ -1348,13 +1415,13 @@
         <v>8</v>
       </c>
       <c r="AY5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ5" t="n">
         <v>4</v>
       </c>
       <c r="BA5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB5" t="n">
         <v>27</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-26-2014-15</t>
+          <t>2015-01-26</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1564,7 @@
         <v>16</v>
       </c>
       <c r="AN6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO6" t="n">
         <v>2</v>
@@ -1530,7 +1597,7 @@
         <v>1</v>
       </c>
       <c r="AY6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ6" t="n">
         <v>3</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-26-2014-15</t>
+          <t>2015-01-26</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>1.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE7" t="n">
         <v>13</v>
@@ -1661,10 +1728,10 @@
         <v>13</v>
       </c>
       <c r="AH7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ7" t="n">
         <v>21</v>
@@ -1679,16 +1746,16 @@
         <v>10</v>
       </c>
       <c r="AN7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AR7" t="n">
         <v>12</v>
@@ -1697,7 +1764,7 @@
         <v>25</v>
       </c>
       <c r="AT7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU7" t="n">
         <v>12</v>
@@ -1718,7 +1785,7 @@
         <v>1</v>
       </c>
       <c r="BA7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB7" t="n">
         <v>12</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-26-2014-15</t>
+          <t>2015-01-26</t>
         </is>
       </c>
     </row>
@@ -1753,61 +1820,61 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E8" t="n">
         <v>30</v>
       </c>
       <c r="F8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.667</v>
       </c>
       <c r="H8" t="n">
         <v>48.6</v>
       </c>
       <c r="I8" t="n">
-        <v>40.6</v>
+        <v>40.5</v>
       </c>
       <c r="J8" t="n">
-        <v>86.2</v>
+        <v>86</v>
       </c>
       <c r="K8" t="n">
         <v>0.471</v>
       </c>
       <c r="L8" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="M8" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="N8" t="n">
         <v>0.356</v>
       </c>
       <c r="O8" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="P8" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.763</v>
+        <v>0.765</v>
       </c>
       <c r="R8" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S8" t="n">
-        <v>31.4</v>
+        <v>31.3</v>
       </c>
       <c r="T8" t="n">
-        <v>42.2</v>
+        <v>42</v>
       </c>
       <c r="U8" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="V8" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="W8" t="n">
         <v>8</v>
@@ -1825,31 +1892,31 @@
         <v>22.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>108</v>
+        <v>107.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AD8" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AE8" t="n">
         <v>6</v>
       </c>
       <c r="AF8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AK8" t="n">
         <v>5</v>
@@ -1858,16 +1925,16 @@
         <v>7</v>
       </c>
       <c r="AM8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN8" t="n">
         <v>12</v>
       </c>
       <c r="AO8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ8" t="n">
         <v>12</v>
@@ -1876,10 +1943,10 @@
         <v>16</v>
       </c>
       <c r="AS8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT8" t="n">
         <v>21</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>19</v>
       </c>
       <c r="AU8" t="n">
         <v>8</v>
@@ -1891,10 +1958,10 @@
         <v>11</v>
       </c>
       <c r="AX8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ8" t="n">
         <v>15</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-26-2014-15</t>
+          <t>2015-01-26</t>
         </is>
       </c>
     </row>
@@ -1935,61 +2002,61 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E9" t="n">
         <v>18</v>
       </c>
       <c r="F9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4</v>
+        <v>0.409</v>
       </c>
       <c r="H9" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I9" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="J9" t="n">
-        <v>86.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L9" t="n">
         <v>7.6</v>
       </c>
       <c r="M9" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="N9" t="n">
-        <v>0.324</v>
+        <v>0.323</v>
       </c>
       <c r="O9" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="P9" t="n">
-        <v>25.5</v>
+        <v>25.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.735</v>
+        <v>0.736</v>
       </c>
       <c r="R9" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="S9" t="n">
-        <v>33.1</v>
+        <v>33.2</v>
       </c>
       <c r="T9" t="n">
-        <v>45.6</v>
+        <v>45.8</v>
       </c>
       <c r="U9" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="V9" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W9" t="n">
         <v>7</v>
@@ -2001,31 +2068,31 @@
         <v>5.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AB9" t="n">
-        <v>101.8</v>
+        <v>101.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>-2.7</v>
+        <v>-2.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AE9" t="n">
         <v>19</v>
       </c>
       <c r="AF9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AG9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI9" t="n">
         <v>13</v>
@@ -2046,7 +2113,7 @@
         <v>26</v>
       </c>
       <c r="AO9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AP9" t="n">
         <v>3</v>
@@ -2061,13 +2128,13 @@
         <v>10</v>
       </c>
       <c r="AT9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW9" t="n">
         <v>24</v>
@@ -2076,13 +2143,13 @@
         <v>17</v>
       </c>
       <c r="AY9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ9" t="n">
         <v>30</v>
       </c>
       <c r="BA9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-26-2014-15</t>
+          <t>2015-01-26</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-2</v>
       </c>
       <c r="AD10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE10" t="n">
         <v>21</v>
@@ -2207,13 +2274,13 @@
         <v>21</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK10" t="n">
         <v>28</v>
@@ -2231,7 +2298,7 @@
         <v>24</v>
       </c>
       <c r="AP10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ10" t="n">
         <v>29</v>
@@ -2255,7 +2322,7 @@
         <v>12</v>
       </c>
       <c r="AX10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY10" t="n">
         <v>16</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-26-2014-15</t>
+          <t>2015-01-26</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>11.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -2395,7 +2462,7 @@
         <v>1</v>
       </c>
       <c r="AJ11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK11" t="n">
         <v>1</v>
@@ -2404,7 +2471,7 @@
         <v>2</v>
       </c>
       <c r="AM11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN11" t="n">
         <v>1</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-26-2014-15</t>
+          <t>2015-01-26</t>
         </is>
       </c>
     </row>
@@ -2481,52 +2548,52 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F12" t="n">
         <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="J12" t="n">
-        <v>83.40000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="K12" t="n">
-        <v>0.441</v>
+        <v>0.44</v>
       </c>
       <c r="L12" t="n">
         <v>11.8</v>
       </c>
       <c r="M12" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0.351</v>
+        <v>0.352</v>
       </c>
       <c r="O12" t="n">
-        <v>17.5</v>
+        <v>17.9</v>
       </c>
       <c r="P12" t="n">
-        <v>24.4</v>
+        <v>24.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.719</v>
+        <v>0.717</v>
       </c>
       <c r="R12" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S12" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="T12" t="n">
         <v>43.4</v>
@@ -2538,7 +2605,7 @@
         <v>17.4</v>
       </c>
       <c r="W12" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="X12" t="n">
         <v>4.5</v>
@@ -2547,40 +2614,40 @@
         <v>5.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.5</v>
+        <v>20.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>102.9</v>
+        <v>103</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AD12" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AE12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AF12" t="n">
         <v>5</v>
       </c>
       <c r="AG12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AI12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL12" t="n">
         <v>1</v>
@@ -2589,49 +2656,49 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AQ12" t="n">
         <v>28</v>
       </c>
       <c r="AR12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AS12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV12" t="n">
         <v>29</v>
       </c>
       <c r="AW12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BA12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BB12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC12" t="n">
         <v>9</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-26-2014-15</t>
+          <t>2015-01-26</t>
         </is>
       </c>
     </row>
@@ -2765,7 +2832,7 @@
         <v>27</v>
       </c>
       <c r="AL13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM13" t="n">
         <v>18</v>
@@ -2780,7 +2847,7 @@
         <v>24</v>
       </c>
       <c r="AQ13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AR13" t="n">
         <v>14</v>
@@ -2807,7 +2874,7 @@
         <v>17</v>
       </c>
       <c r="AZ13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-26-2014-15</t>
+          <t>2015-01-26</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E14" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F14" t="n">
         <v>14</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
@@ -2869,10 +2936,10 @@
         <v>0.475</v>
       </c>
       <c r="L14" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="M14" t="n">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="N14" t="n">
         <v>0.384</v>
@@ -2881,19 +2948,19 @@
         <v>18.9</v>
       </c>
       <c r="P14" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.749</v>
+        <v>0.746</v>
       </c>
       <c r="R14" t="n">
         <v>9</v>
       </c>
       <c r="S14" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="T14" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="U14" t="n">
         <v>25.1</v>
@@ -2911,28 +2978,28 @@
         <v>3</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.3</v>
+        <v>107.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AE14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF14" t="n">
         <v>5</v>
       </c>
       <c r="AG14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH14" t="n">
         <v>26</v>
@@ -2950,19 +3017,19 @@
         <v>4</v>
       </c>
       <c r="AM14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AN14" t="n">
         <v>3</v>
       </c>
       <c r="AO14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP14" t="n">
         <v>5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR14" t="n">
         <v>27</v>
@@ -2971,7 +3038,7 @@
         <v>15</v>
       </c>
       <c r="AT14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU14" t="n">
         <v>3</v>
@@ -2983,7 +3050,7 @@
         <v>13</v>
       </c>
       <c r="AX14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AY14" t="n">
         <v>1</v>
@@ -2992,13 +3059,13 @@
         <v>16</v>
       </c>
       <c r="BA14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-26-2014-15</t>
+          <t>2015-01-26</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E15" t="n">
         <v>12</v>
       </c>
       <c r="F15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G15" t="n">
-        <v>0.273</v>
+        <v>0.267</v>
       </c>
       <c r="H15" t="n">
         <v>48.3</v>
       </c>
       <c r="I15" t="n">
-        <v>37.2</v>
+        <v>37</v>
       </c>
       <c r="J15" t="n">
-        <v>85.2</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.437</v>
+        <v>0.435</v>
       </c>
       <c r="L15" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M15" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="N15" t="n">
-        <v>0.349</v>
+        <v>0.348</v>
       </c>
       <c r="O15" t="n">
-        <v>18.2</v>
+        <v>18.5</v>
       </c>
       <c r="P15" t="n">
-        <v>24.5</v>
+        <v>24.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.743</v>
+        <v>0.744</v>
       </c>
       <c r="R15" t="n">
         <v>11.4</v>
       </c>
       <c r="S15" t="n">
-        <v>31.9</v>
+        <v>31.7</v>
       </c>
       <c r="T15" t="n">
-        <v>43.3</v>
+        <v>43.1</v>
       </c>
       <c r="U15" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V15" t="n">
         <v>13.1</v>
@@ -3087,31 +3154,31 @@
         <v>7.3</v>
       </c>
       <c r="X15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y15" t="n">
         <v>4.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>21</v>
+        <v>21.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.5</v>
+        <v>99.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.6</v>
+        <v>-6.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
       </c>
       <c r="AF15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG15" t="n">
         <v>27</v>
@@ -3120,16 +3187,16 @@
         <v>18</v>
       </c>
       <c r="AI15" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AJ15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AK15" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AL15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM15" t="n">
         <v>22</v>
@@ -3138,13 +3205,13 @@
         <v>15</v>
       </c>
       <c r="AO15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AP15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AR15" t="n">
         <v>11</v>
@@ -3156,25 +3223,25 @@
         <v>15</v>
       </c>
       <c r="AU15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX15" t="n">
         <v>22</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>21</v>
       </c>
       <c r="AY15" t="n">
         <v>9</v>
       </c>
       <c r="AZ15" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA15" t="n">
         <v>17</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>20</v>
       </c>
       <c r="BB15" t="n">
         <v>19</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-26-2014-15</t>
+          <t>2015-01-26</t>
         </is>
       </c>
     </row>
@@ -3209,25 +3276,25 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E16" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F16" t="n">
         <v>12</v>
       </c>
       <c r="G16" t="n">
-        <v>0.727</v>
+        <v>0.721</v>
       </c>
       <c r="H16" t="n">
         <v>49</v>
       </c>
       <c r="I16" t="n">
-        <v>38.7</v>
+        <v>38.8</v>
       </c>
       <c r="J16" t="n">
-        <v>83.3</v>
+        <v>83.5</v>
       </c>
       <c r="K16" t="n">
         <v>0.465</v>
@@ -3236,19 +3303,19 @@
         <v>5.5</v>
       </c>
       <c r="M16" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="N16" t="n">
-        <v>0.348</v>
+        <v>0.347</v>
       </c>
       <c r="O16" t="n">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="P16" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.78</v>
+        <v>0.777</v>
       </c>
       <c r="R16" t="n">
         <v>10.3</v>
@@ -3257,16 +3324,16 @@
         <v>32.5</v>
       </c>
       <c r="T16" t="n">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="U16" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="V16" t="n">
         <v>13.1</v>
       </c>
       <c r="W16" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X16" t="n">
         <v>4.5</v>
@@ -3278,19 +3345,19 @@
         <v>19.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AB16" t="n">
         <v>101.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="AE16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF16" t="n">
         <v>3</v>
@@ -3305,7 +3372,7 @@
         <v>7</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AK16" t="n">
         <v>7</v>
@@ -3320,16 +3387,16 @@
         <v>16</v>
       </c>
       <c r="AO16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP16" t="n">
         <v>13</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS16" t="n">
         <v>14</v>
@@ -3338,16 +3405,16 @@
         <v>16</v>
       </c>
       <c r="AU16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW16" t="n">
         <v>8</v>
       </c>
       <c r="AX16" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY16" t="n">
         <v>20</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-26-2014-15</t>
+          <t>2015-01-26</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-3.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
@@ -3502,13 +3569,13 @@
         <v>21</v>
       </c>
       <c r="AO17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP17" t="n">
         <v>11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
@@ -3523,7 +3590,7 @@
         <v>28</v>
       </c>
       <c r="AV17" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AW17" t="n">
         <v>9</v>
@@ -3538,7 +3605,7 @@
         <v>13</v>
       </c>
       <c r="BA17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB17" t="n">
         <v>28</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-26-2014-15</t>
+          <t>2015-01-26</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3718,16 @@
         <v>1.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF18" t="n">
         <v>15</v>
       </c>
       <c r="AG18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH18" t="n">
         <v>7</v>
@@ -3699,7 +3766,7 @@
         <v>24</v>
       </c>
       <c r="AT18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU18" t="n">
         <v>7</v>
@@ -3714,7 +3781,7 @@
         <v>15</v>
       </c>
       <c r="AY18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ18" t="n">
         <v>29</v>
@@ -3726,7 +3793,7 @@
         <v>20</v>
       </c>
       <c r="BC18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-26-2014-15</t>
+          <t>2015-01-26</t>
         </is>
       </c>
     </row>
@@ -3755,58 +3822,58 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E19" t="n">
         <v>7</v>
       </c>
       <c r="F19" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G19" t="n">
-        <v>0.159</v>
+        <v>0.163</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
       </c>
       <c r="I19" t="n">
-        <v>36.9</v>
+        <v>37.1</v>
       </c>
       <c r="J19" t="n">
         <v>85.09999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.434</v>
+        <v>0.436</v>
       </c>
       <c r="L19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="M19" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0.334</v>
+        <v>0.337</v>
       </c>
       <c r="O19" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="P19" t="n">
-        <v>24.7</v>
+        <v>24.5</v>
       </c>
       <c r="Q19" t="n">
         <v>0.744</v>
       </c>
       <c r="R19" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="S19" t="n">
-        <v>28.7</v>
+        <v>28.5</v>
       </c>
       <c r="T19" t="n">
-        <v>40.9</v>
+        <v>40.7</v>
       </c>
       <c r="U19" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="V19" t="n">
         <v>15.1</v>
@@ -3818,22 +3885,22 @@
         <v>4.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Z19" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>97.3</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC19" t="n">
         <v>-9.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="AE19" t="n">
         <v>30</v>
@@ -3848,13 +3915,13 @@
         <v>21</v>
       </c>
       <c r="AI19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK19" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL19" t="n">
         <v>30</v>
@@ -3866,13 +3933,13 @@
         <v>22</v>
       </c>
       <c r="AO19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP19" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AQ19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR19" t="n">
         <v>3</v>
@@ -3884,7 +3951,7 @@
         <v>27</v>
       </c>
       <c r="AU19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV19" t="n">
         <v>24</v>
@@ -3893,10 +3960,10 @@
         <v>7</v>
       </c>
       <c r="AX19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ19" t="n">
         <v>11</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-26-2014-15</t>
+          <t>2015-01-26</t>
         </is>
       </c>
     </row>
@@ -3952,13 +4019,13 @@
         <v>48.2</v>
       </c>
       <c r="I20" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="J20" t="n">
-        <v>83.5</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L20" t="n">
         <v>6.5</v>
@@ -3967,37 +4034,37 @@
         <v>18.9</v>
       </c>
       <c r="N20" t="n">
-        <v>0.345</v>
+        <v>0.341</v>
       </c>
       <c r="O20" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="P20" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.763</v>
+        <v>0.755</v>
       </c>
       <c r="R20" t="n">
-        <v>11.6</v>
+        <v>11.8</v>
       </c>
       <c r="S20" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="T20" t="n">
-        <v>43.5</v>
+        <v>43.8</v>
       </c>
       <c r="U20" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="V20" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="W20" t="n">
         <v>7.2</v>
       </c>
       <c r="X20" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="Y20" t="n">
         <v>5.9</v>
@@ -4006,16 +4073,16 @@
         <v>19.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>100.3</v>
+        <v>100.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE20" t="n">
         <v>14</v>
@@ -4027,7 +4094,7 @@
         <v>14</v>
       </c>
       <c r="AH20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI20" t="n">
         <v>10</v>
@@ -4036,7 +4103,7 @@
         <v>14</v>
       </c>
       <c r="AK20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL20" t="n">
         <v>25</v>
@@ -4045,31 +4112,31 @@
         <v>24</v>
       </c>
       <c r="AN20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP20" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AQ20" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS20" t="n">
         <v>17</v>
       </c>
       <c r="AT20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW20" t="n">
         <v>22</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-26-2014-15</t>
+          <t>2015-01-26</t>
         </is>
       </c>
     </row>
@@ -4197,31 +4264,31 @@
         <v>-8</v>
       </c>
       <c r="AD21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE21" t="n">
         <v>28</v>
       </c>
       <c r="AF21" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AG21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AH21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI21" t="n">
         <v>26</v>
       </c>
       <c r="AJ21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK21" t="n">
         <v>23</v>
       </c>
       <c r="AL21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM21" t="n">
         <v>20</v>
@@ -4239,7 +4306,7 @@
         <v>10</v>
       </c>
       <c r="AR21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS21" t="n">
         <v>28</v>
@@ -4248,7 +4315,7 @@
         <v>29</v>
       </c>
       <c r="AU21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV21" t="n">
         <v>20</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-26-2014-15</t>
+          <t>2015-01-26</t>
         </is>
       </c>
     </row>
@@ -4301,19 +4368,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F22" t="n">
         <v>22</v>
       </c>
       <c r="G22" t="n">
-        <v>0.511</v>
+        <v>0.5</v>
       </c>
       <c r="H22" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I22" t="n">
         <v>37.5</v>
@@ -4322,7 +4389,7 @@
         <v>85.2</v>
       </c>
       <c r="K22" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="L22" t="n">
         <v>7.4</v>
@@ -4331,28 +4398,28 @@
         <v>23</v>
       </c>
       <c r="N22" t="n">
-        <v>0.32</v>
+        <v>0.322</v>
       </c>
       <c r="O22" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="P22" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.74</v>
+        <v>0.741</v>
       </c>
       <c r="R22" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="S22" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="T22" t="n">
-        <v>46.6</v>
+        <v>46.5</v>
       </c>
       <c r="U22" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="V22" t="n">
         <v>14.9</v>
@@ -4361,7 +4428,7 @@
         <v>7.3</v>
       </c>
       <c r="X22" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Y22" t="n">
         <v>4.6</v>
@@ -4370,19 +4437,19 @@
         <v>22.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AE22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF22" t="n">
         <v>15</v>
@@ -4391,19 +4458,19 @@
         <v>15</v>
       </c>
       <c r="AH22" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI22" t="n">
         <v>15</v>
       </c>
       <c r="AJ22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM22" t="n">
         <v>14</v>
@@ -4418,10 +4485,10 @@
         <v>14</v>
       </c>
       <c r="AQ22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS22" t="n">
         <v>3</v>
@@ -4436,25 +4503,25 @@
         <v>22</v>
       </c>
       <c r="AW22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY22" t="n">
         <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-26-2014-15</t>
+          <t>2015-01-26</t>
         </is>
       </c>
     </row>
@@ -4498,13 +4565,13 @@
         <v>48.1</v>
       </c>
       <c r="I23" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J23" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="K23" t="n">
-        <v>0.458</v>
+        <v>0.456</v>
       </c>
       <c r="L23" t="n">
         <v>7</v>
@@ -4513,25 +4580,25 @@
         <v>19.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0.364</v>
+        <v>0.365</v>
       </c>
       <c r="O23" t="n">
         <v>14.2</v>
       </c>
       <c r="P23" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.73</v>
+        <v>0.733</v>
       </c>
       <c r="R23" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>31.5</v>
+        <v>31.7</v>
       </c>
       <c r="T23" t="n">
-        <v>40.1</v>
+        <v>40.4</v>
       </c>
       <c r="U23" t="n">
         <v>20.5</v>
@@ -4540,31 +4607,31 @@
         <v>14.7</v>
       </c>
       <c r="W23" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X23" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="Z23" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA23" t="n">
         <v>18.6</v>
       </c>
       <c r="AB23" t="n">
-        <v>96</v>
+        <v>95.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.7</v>
+        <v>-5.9</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
       </c>
       <c r="AE23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF23" t="n">
         <v>26</v>
@@ -4579,13 +4646,13 @@
         <v>16</v>
       </c>
       <c r="AJ23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK23" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AL23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM23" t="n">
         <v>23</v>
@@ -4600,7 +4667,7 @@
         <v>29</v>
       </c>
       <c r="AQ23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR23" t="n">
         <v>28</v>
@@ -4612,28 +4679,28 @@
         <v>28</v>
       </c>
       <c r="AU23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV23" t="n">
         <v>19</v>
       </c>
       <c r="AW23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX23" t="n">
         <v>30</v>
       </c>
       <c r="AY23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AZ23" t="n">
         <v>21</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>22</v>
       </c>
       <c r="BA23" t="n">
         <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC23" t="n">
         <v>26</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-26-2014-15</t>
+          <t>2015-01-26</t>
         </is>
       </c>
     </row>
@@ -4665,37 +4732,37 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E24" t="n">
         <v>8</v>
       </c>
       <c r="F24" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G24" t="n">
-        <v>0.178</v>
+        <v>0.182</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
       </c>
       <c r="I24" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="J24" t="n">
         <v>81</v>
       </c>
       <c r="K24" t="n">
-        <v>0.407</v>
+        <v>0.408</v>
       </c>
       <c r="L24" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="M24" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="N24" t="n">
-        <v>0.297</v>
+        <v>0.299</v>
       </c>
       <c r="O24" t="n">
         <v>16.6</v>
@@ -4704,22 +4771,22 @@
         <v>24.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.681</v>
+        <v>0.679</v>
       </c>
       <c r="R24" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="S24" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="T24" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="U24" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="V24" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="W24" t="n">
         <v>9.800000000000001</v>
@@ -4728,22 +4795,22 @@
         <v>5.9</v>
       </c>
       <c r="Y24" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z24" t="n">
         <v>21.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>89.5</v>
+        <v>89.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>-12.8</v>
+        <v>-12.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4755,7 +4822,7 @@
         <v>28</v>
       </c>
       <c r="AH24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI24" t="n">
         <v>30</v>
@@ -4767,7 +4834,7 @@
         <v>30</v>
       </c>
       <c r="AL24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM24" t="n">
         <v>11</v>
@@ -4785,7 +4852,7 @@
         <v>30</v>
       </c>
       <c r="AR24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS24" t="n">
         <v>27</v>
@@ -4800,19 +4867,19 @@
         <v>30</v>
       </c>
       <c r="AW24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX24" t="n">
         <v>3</v>
       </c>
       <c r="AY24" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AZ24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-26-2014-15</t>
+          <t>2015-01-26</t>
         </is>
       </c>
     </row>
@@ -4943,7 +5010,7 @@
         <v>3</v>
       </c>
       <c r="AJ25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK25" t="n">
         <v>6</v>
@@ -4958,7 +5025,7 @@
         <v>10</v>
       </c>
       <c r="AO25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP25" t="n">
         <v>22</v>
@@ -4967,7 +5034,7 @@
         <v>2</v>
       </c>
       <c r="AR25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS25" t="n">
         <v>19</v>
@@ -4991,13 +5058,13 @@
         <v>5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA25" t="n">
         <v>13</v>
       </c>
       <c r="BB25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC25" t="n">
         <v>12</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-26-2014-15</t>
+          <t>2015-01-26</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>5.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE26" t="n">
         <v>3</v>
@@ -5119,7 +5186,7 @@
         <v>4</v>
       </c>
       <c r="AH26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI26" t="n">
         <v>9</v>
@@ -5155,7 +5222,7 @@
         <v>1</v>
       </c>
       <c r="AT26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU26" t="n">
         <v>9</v>
@@ -5176,7 +5243,7 @@
         <v>6</v>
       </c>
       <c r="BA26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB26" t="n">
         <v>7</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-26-2014-15</t>
+          <t>2015-01-26</t>
         </is>
       </c>
     </row>
@@ -5289,13 +5356,13 @@
         <v>-2.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE27" t="n">
         <v>22</v>
       </c>
       <c r="AF27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG27" t="n">
         <v>22</v>
@@ -5304,7 +5371,7 @@
         <v>4</v>
       </c>
       <c r="AI27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ27" t="n">
         <v>28</v>
@@ -5334,7 +5401,7 @@
         <v>13</v>
       </c>
       <c r="AS27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT27" t="n">
         <v>7</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-26-2014-15</t>
+          <t>2015-01-26</t>
         </is>
       </c>
     </row>
@@ -5393,43 +5460,43 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E28" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F28" t="n">
         <v>17</v>
       </c>
       <c r="G28" t="n">
-        <v>0.622</v>
+        <v>0.63</v>
       </c>
       <c r="H28" t="n">
         <v>49</v>
       </c>
       <c r="I28" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="J28" t="n">
-        <v>83.40000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L28" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>22.1</v>
+        <v>22.3</v>
       </c>
       <c r="N28" t="n">
-        <v>0.365</v>
+        <v>0.369</v>
       </c>
       <c r="O28" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P28" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="Q28" t="n">
         <v>0.767</v>
@@ -5438,22 +5505,22 @@
         <v>10</v>
       </c>
       <c r="S28" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="T28" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="U28" t="n">
         <v>24.3</v>
       </c>
       <c r="V28" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="W28" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y28" t="n">
         <v>4.8</v>
@@ -5468,19 +5535,19 @@
         <v>101.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AD28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AF28" t="n">
         <v>10</v>
       </c>
       <c r="AG28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH28" t="n">
         <v>2</v>
@@ -5489,10 +5556,10 @@
         <v>12</v>
       </c>
       <c r="AJ28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK28" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AL28" t="n">
         <v>11</v>
@@ -5501,13 +5568,13 @@
         <v>15</v>
       </c>
       <c r="AN28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO28" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AP28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ28" t="n">
         <v>11</v>
@@ -5516,19 +5583,19 @@
         <v>25</v>
       </c>
       <c r="AS28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AW28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX28" t="n">
         <v>7</v>
@@ -5540,7 +5607,7 @@
         <v>9</v>
       </c>
       <c r="BA28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB28" t="n">
         <v>15</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-26-2014-15</t>
+          <t>2015-01-26</t>
         </is>
       </c>
     </row>
@@ -5653,13 +5720,13 @@
         <v>5</v>
       </c>
       <c r="AD29" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE29" t="n">
         <v>9</v>
       </c>
       <c r="AF29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG29" t="n">
         <v>9</v>
@@ -5674,7 +5741,7 @@
         <v>12</v>
       </c>
       <c r="AK29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL29" t="n">
         <v>9</v>
@@ -5692,7 +5759,7 @@
         <v>4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR29" t="n">
         <v>9</v>
@@ -5701,7 +5768,7 @@
         <v>26</v>
       </c>
       <c r="AT29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU29" t="n">
         <v>19</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-26-2014-15</t>
+          <t>2015-01-26</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E30" t="n">
         <v>16</v>
       </c>
       <c r="F30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G30" t="n">
-        <v>0.356</v>
+        <v>0.364</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
@@ -5775,37 +5842,37 @@
         <v>35.6</v>
       </c>
       <c r="J30" t="n">
-        <v>79</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>0.451</v>
+        <v>0.452</v>
       </c>
       <c r="L30" t="n">
         <v>7.2</v>
       </c>
       <c r="M30" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="N30" t="n">
-        <v>0.344</v>
+        <v>0.343</v>
       </c>
       <c r="O30" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="P30" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.75</v>
+        <v>0.753</v>
       </c>
       <c r="R30" t="n">
         <v>11.5</v>
       </c>
       <c r="S30" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="T30" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="U30" t="n">
         <v>20.4</v>
@@ -5817,34 +5884,34 @@
         <v>6.9</v>
       </c>
       <c r="X30" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Y30" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z30" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="AA30" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>95.7</v>
+        <v>95.8</v>
       </c>
       <c r="AC30" t="n">
-        <v>-2.8</v>
+        <v>-2.7</v>
       </c>
       <c r="AD30" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AE30" t="n">
         <v>22</v>
       </c>
       <c r="AF30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH30" t="n">
         <v>29</v>
@@ -5856,7 +5923,7 @@
         <v>29</v>
       </c>
       <c r="AK30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL30" t="n">
         <v>17</v>
@@ -5865,16 +5932,16 @@
         <v>17</v>
       </c>
       <c r="AN30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO30" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AP30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ30" t="n">
         <v>16</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>17</v>
       </c>
       <c r="AR30" t="n">
         <v>10</v>
@@ -5904,10 +5971,10 @@
         <v>5</v>
       </c>
       <c r="BA30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC30" t="n">
         <v>23</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-26-2014-15</t>
+          <t>2015-01-26</t>
         </is>
       </c>
     </row>
@@ -6017,19 +6084,19 @@
         <v>2.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE31" t="n">
         <v>6</v>
       </c>
       <c r="AF31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI31" t="n">
         <v>6</v>
@@ -6056,19 +6123,19 @@
         <v>25</v>
       </c>
       <c r="AQ31" t="n">
+        <v>24</v>
+      </c>
+      <c r="AR31" t="n">
         <v>23</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>22</v>
       </c>
       <c r="AS31" t="n">
         <v>9</v>
       </c>
       <c r="AT31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV31" t="n">
         <v>20</v>
@@ -6077,19 +6144,19 @@
         <v>14</v>
       </c>
       <c r="AX31" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AY31" t="n">
         <v>7</v>
       </c>
       <c r="AZ31" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA31" t="n">
         <v>19</v>
       </c>
-      <c r="BA31" t="n">
+      <c r="BB31" t="n">
         <v>18</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>17</v>
       </c>
       <c r="BC31" t="n">
         <v>11</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-26-2014-15</t>
+          <t>2015-01-26</t>
         </is>
       </c>
     </row>
